--- a/docs/assets/Capstone-Project-Final-Evaluation-2026.xlsx
+++ b/docs/assets/Capstone-Project-Final-Evaluation-2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10420"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10526"/>
   <workbookPr showInkAnnotation="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ernesto/github/MHACapstone/docs/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFD6D5AA-44E8-F14C-9BE3-1E4AAB8771F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{838378A2-DA84-E04C-B9BF-06CFBF293DDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25680" yWindow="660" windowWidth="25360" windowHeight="27980" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25680" yWindow="680" windowWidth="25360" windowHeight="27980" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OVERALL GRADE" sheetId="3" r:id="rId1"/>
@@ -303,7 +303,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="121">
   <si>
     <t>Final Capstone Project Evaluation Form</t>
   </si>
@@ -452,12 +452,6 @@
     <t xml:space="preserve">Note: Please refer to the linked rubrics and guidelines (links underlined below) for your evaluation. </t>
   </si>
   <si>
-    <t xml:space="preserve">Note: this portion of the evaluation represents 85% of the final grade </t>
-  </si>
-  <si>
-    <t>Part 1 - Written Report (guidelines) - 70%</t>
-  </si>
-  <si>
     <t>Written Report Grading Rubric</t>
   </si>
   <si>
@@ -516,9 +510,6 @@
   </si>
   <si>
     <t>Converted Percentage</t>
-  </si>
-  <si>
-    <t>Part 2 - Poster Presentation (guidelines) - 30%</t>
   </si>
   <si>
     <t>Poster Grading Rubric</t>
@@ -578,12 +569,6 @@
     <t xml:space="preserve">... was able to work independently. </t>
   </si>
   <si>
-    <t xml:space="preserve">... set and met internal deadlines to keep his/her project on task. </t>
-  </si>
-  <si>
-    <t>... was professional and punctual in face-to-face meetings with committee members.</t>
-  </si>
-  <si>
     <t>... was professional and punctual in email exchanges with committee members.</t>
   </si>
   <si>
@@ -681,6 +666,27 @@
   </si>
   <si>
     <t>Answering Questions</t>
+  </si>
+  <si>
+    <t>... was professional and punctual in meetings and communications.</t>
+  </si>
+  <si>
+    <t>... Asked questions and kept diligent notes.</t>
+  </si>
+  <si>
+    <t>... exhibited progressive improvement and academic growth, culminating in a master of the capstone topic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">... set and met internal deadlines to keep the project on task. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">This portion of the evaluation represents 80% of the final grade </t>
+  </si>
+  <si>
+    <t>Part 1 - Written Report (guidelines)</t>
+  </si>
+  <si>
+    <t>Part 2 - Poster Presentation (guidelines)</t>
   </si>
 </sst>
 </file>
@@ -1358,8 +1364,9 @@
     <xf numFmtId="49" fontId="8" fillId="12" borderId="3" xfId="18" applyNumberFormat="1" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="8" fillId="12" borderId="6" xfId="18" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="7" fillId="10" borderId="9" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="25">
@@ -1729,6 +1736,9 @@
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table3" displayName="Table3" ref="A24:C36" totalsRowShown="0" headerRowDxfId="8">
   <autoFilter ref="A24:C36" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A25:C36">
+    <sortCondition descending="1" ref="B24:B36"/>
+  </sortState>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Letter grade"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Percentage"/>
@@ -1741,8 +1751,8 @@
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table2" displayName="Table2" ref="G8:I19" totalsRowShown="0" dataDxfId="7" headerRowCellStyle="Accent1">
   <autoFilter ref="G8:I19" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="G7:G15">
-    <sortCondition ref="G6:G15"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="G9:I19">
+    <sortCondition descending="1" ref="G8:G19"/>
   </sortState>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Score" dataDxfId="6"/>
@@ -1765,8 +1775,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Table4" displayName="Table4" ref="A11:B25" totalsRowShown="0" headerRowCellStyle="Accent1">
-  <autoFilter ref="A11:B25" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Table4" displayName="Table4" ref="A11:B24" totalsRowShown="0" headerRowCellStyle="Accent1">
+  <autoFilter ref="A11:B24" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="2">
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="The Student…" dataDxfId="1"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Score_x000a_Range: 0-1" dataDxfId="0"/>
@@ -2065,12 +2075,12 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="48" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -2162,20 +2172,20 @@
         <v>13</v>
       </c>
       <c r="B14" s="9" t="e">
-        <f>'Mentor Evaluation'!B25</f>
+        <f>'Mentor Evaluation'!B24</f>
         <v>#DIV/0!</v>
       </c>
       <c r="C14">
         <v>5</v>
       </c>
       <c r="D14" s="6">
-        <f>COUNTBLANK('Mentor Evaluation'!B12:B23)</f>
-        <v>12</v>
+        <f>COUNTBLANK('Mentor Evaluation'!B12:B22)</f>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="52" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B15" s="9" t="e">
         <f>'Chair Evaluation'!B23</f>
@@ -2191,7 +2201,7 @@
     </row>
     <row r="16" spans="1:4" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B16" s="53"/>
       <c r="C16">
@@ -2224,7 +2234,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
@@ -2249,135 +2259,135 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="36" t="s">
-        <v>21</v>
-      </c>
-      <c r="B25" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="C25" s="36">
-        <v>0</v>
+      <c r="A25" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25" s="38">
+        <v>93</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="36" t="s">
-        <v>23</v>
-      </c>
-      <c r="B26" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="36">
-        <v>60</v>
+      <c r="A26" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" s="38">
+        <v>90</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="36" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" s="36" t="s">
-        <v>26</v>
-      </c>
-      <c r="C27" s="36">
-        <v>63</v>
+      <c r="A27" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="37" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" s="37">
+        <v>87</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="36" t="s">
-        <v>27</v>
-      </c>
-      <c r="B28" s="36" t="s">
-        <v>28</v>
-      </c>
-      <c r="C28" s="36">
-        <v>67</v>
+      <c r="A28" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="C28" s="37">
+        <v>83</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="B29" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="C29" s="36">
-        <v>70</v>
+      <c r="A29" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="C29" s="37">
+        <v>80</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="36" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B30" s="36" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C30" s="36">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="36" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B31" s="36" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C31" s="36">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="37" t="s">
-        <v>35</v>
-      </c>
-      <c r="B32" s="37" t="s">
-        <v>36</v>
-      </c>
-      <c r="C32" s="37">
-        <v>80</v>
+      <c r="A32" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="B32" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="C32" s="36">
+        <v>70</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33" s="37" t="s">
-        <v>37</v>
-      </c>
-      <c r="B33" s="37" t="s">
-        <v>38</v>
-      </c>
-      <c r="C33" s="37">
-        <v>83</v>
+      <c r="A33" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="B33" s="36" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" s="36">
+        <v>67</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A34" s="37" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" s="37" t="s">
-        <v>40</v>
-      </c>
-      <c r="C34" s="37">
-        <v>87</v>
+      <c r="A34" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="B34" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="C34" s="36">
+        <v>63</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A35" s="38" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" s="38" t="s">
-        <v>42</v>
-      </c>
-      <c r="C35" s="38">
-        <v>90</v>
+      <c r="A35" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="B35" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="C35" s="36">
+        <v>60</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A36" s="38" t="s">
-        <v>43</v>
-      </c>
-      <c r="B36" s="38" t="s">
-        <v>44</v>
-      </c>
-      <c r="C36" s="38">
-        <v>93</v>
+      <c r="A36" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="B36" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="C36" s="36">
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
@@ -2473,13 +2483,13 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>49</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="2" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="61"/>
       <c r="B8" s="62" t="s">
-        <v>50</v>
+        <v>119</v>
       </c>
       <c r="C8" s="63" t="str">
         <f>'OVERALL GRADE'!A8</f>
@@ -2498,15 +2508,15 @@
         <v>9</v>
       </c>
       <c r="H8" s="55" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="I8" s="25" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="B9" s="60" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C9" s="7">
         <f>'OVERALL GRADE'!B8</f>
@@ -2520,34 +2530,34 @@
         <f>'OVERALL GRADE'!B10</f>
         <v>0</v>
       </c>
-      <c r="G9" s="33">
-        <v>0</v>
-      </c>
-      <c r="H9" s="56" t="s">
-        <v>21</v>
-      </c>
-      <c r="I9" s="30" t="s">
-        <v>57</v>
+      <c r="G9" s="35">
+        <v>10</v>
+      </c>
+      <c r="H9" s="58" t="s">
+        <v>43</v>
+      </c>
+      <c r="I9" s="32" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="19" x14ac:dyDescent="0.2">
       <c r="C10" s="73" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="73" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" s="73" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="73" t="s">
-        <v>53</v>
-      </c>
-      <c r="E10" s="73" t="s">
-        <v>54</v>
-      </c>
-      <c r="G10" s="33">
-        <v>7.9</v>
-      </c>
-      <c r="H10" s="56" t="s">
-        <v>33</v>
-      </c>
-      <c r="I10" s="30" t="s">
-        <v>59</v>
+      <c r="G10" s="35">
+        <v>9.5</v>
+      </c>
+      <c r="H10" s="58" t="s">
+        <v>43</v>
+      </c>
+      <c r="I10" s="32" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:9" s="2" customFormat="1" ht="20" thickBot="1" x14ac:dyDescent="0.25">
@@ -2556,23 +2566,23 @@
         <v>8</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F11"/>
-      <c r="G11" s="34">
-        <v>8</v>
-      </c>
-      <c r="H11" s="57" t="s">
-        <v>35</v>
-      </c>
-      <c r="I11" s="31" t="s">
-        <v>61</v>
+      <c r="G11" s="35">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="H11" s="58" t="s">
+        <v>43</v>
+      </c>
+      <c r="I11" s="32" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -2580,39 +2590,37 @@
         <v>43</v>
       </c>
       <c r="B12" s="67" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C12" s="46"/>
       <c r="D12" s="46"/>
       <c r="E12" s="46"/>
-      <c r="G12" s="34">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="H12" s="57" t="s">
-        <v>35</v>
-      </c>
-      <c r="I12" s="31" t="s">
-        <v>107</v>
-      </c>
+      <c r="G12" s="35">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="H12" s="58" t="s">
+        <v>41</v>
+      </c>
+      <c r="I12" s="45"/>
     </row>
     <row r="13" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
         <v>37</v>
       </c>
       <c r="B13" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C13" s="46"/>
       <c r="D13" s="46"/>
       <c r="E13" s="46"/>
-      <c r="G13" s="34">
-        <v>8.5</v>
-      </c>
-      <c r="H13" s="57" t="s">
-        <v>37</v>
-      </c>
-      <c r="I13" s="31" t="s">
-        <v>108</v>
+      <c r="G13" s="35">
+        <v>9</v>
+      </c>
+      <c r="H13" s="58" t="s">
+        <v>41</v>
+      </c>
+      <c r="I13" s="32" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -2620,7 +2628,7 @@
         <v>31</v>
       </c>
       <c r="B14" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="46"/>
@@ -2632,7 +2640,7 @@
         <v>39</v>
       </c>
       <c r="I14" s="31" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -2640,83 +2648,85 @@
         <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C15" s="46"/>
       <c r="D15" s="46"/>
       <c r="E15" s="46"/>
-      <c r="G15" s="35">
-        <v>9</v>
-      </c>
-      <c r="H15" s="58" t="s">
-        <v>41</v>
-      </c>
-      <c r="I15" s="32" t="s">
-        <v>111</v>
+      <c r="G15" s="34">
+        <v>8.5</v>
+      </c>
+      <c r="H15" s="57" t="s">
+        <v>37</v>
+      </c>
+      <c r="I15" s="31" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C16" s="46"/>
       <c r="D16" s="46"/>
       <c r="E16" s="46"/>
-      <c r="G16" s="35">
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="H16" s="58" t="s">
-        <v>41</v>
-      </c>
-      <c r="I16" s="45"/>
+      <c r="G16" s="34">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="H16" s="57" t="s">
+        <v>35</v>
+      </c>
+      <c r="I16" s="31" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="17" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C17" s="46"/>
       <c r="D17" s="46"/>
       <c r="E17" s="46"/>
-      <c r="G17" s="35">
-        <v>9.3000000000000007</v>
-      </c>
-      <c r="H17" s="58" t="s">
-        <v>43</v>
-      </c>
-      <c r="I17" s="32" t="s">
-        <v>113</v>
+      <c r="G17" s="34">
+        <v>8</v>
+      </c>
+      <c r="H17" s="57" t="s">
+        <v>35</v>
+      </c>
+      <c r="I17" s="31" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C18" s="46"/>
       <c r="D18" s="46"/>
       <c r="E18" s="46"/>
-      <c r="G18" s="35">
-        <v>9.5</v>
-      </c>
-      <c r="H18" s="58" t="s">
-        <v>43</v>
-      </c>
-      <c r="I18" s="32" t="s">
-        <v>109</v>
+      <c r="G18" s="33">
+        <v>7.9</v>
+      </c>
+      <c r="H18" s="56" t="s">
+        <v>33</v>
+      </c>
+      <c r="I18" s="30" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A19" s="17"/>
       <c r="B19" s="18" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C19" s="28" t="e">
         <f>AVERAGE(C12:C18)</f>
@@ -2730,20 +2740,20 @@
         <f>AVERAGE(E12:E18)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G19" s="35">
-        <v>10</v>
-      </c>
-      <c r="H19" s="58" t="s">
-        <v>43</v>
-      </c>
-      <c r="I19" s="32" t="s">
-        <v>68</v>
+      <c r="G19" s="33">
+        <v>0</v>
+      </c>
+      <c r="H19" s="56" t="s">
+        <v>21</v>
+      </c>
+      <c r="I19" s="30" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="17"/>
       <c r="B20" s="18" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C20" s="26" t="e">
         <f>C19/10</f>
@@ -2761,7 +2771,7 @@
     <row r="22" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="61"/>
       <c r="B22" s="64" t="s">
-        <v>71</v>
+        <v>120</v>
       </c>
       <c r="C22" s="61"/>
       <c r="D22" s="61"/>
@@ -2772,16 +2782,16 @@
     <row r="23" spans="1:9" s="2" customFormat="1" ht="19" x14ac:dyDescent="0.2">
       <c r="A23" s="22"/>
       <c r="B23" s="60" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C23" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="E23" s="20" t="s">
         <v>52</v>
-      </c>
-      <c r="D23" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="E23" s="20" t="s">
-        <v>54</v>
       </c>
       <c r="F23"/>
       <c r="G23"/>
@@ -2794,13 +2804,13 @@
         <v>8</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D24" s="21" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -2808,40 +2818,40 @@
         <v>43</v>
       </c>
       <c r="B25" s="67" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C25" s="46"/>
       <c r="D25" s="46"/>
       <c r="E25" s="46"/>
     </row>
     <row r="26" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="80" t="s">
+      <c r="A26" s="69" t="s">
         <v>37</v>
       </c>
       <c r="B26" s="43" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C26" s="46"/>
       <c r="D26" s="46"/>
       <c r="E26" s="46"/>
     </row>
     <row r="27" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="80" t="s">
+      <c r="A27" s="69" t="s">
         <v>31</v>
       </c>
       <c r="B27" s="43" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C27" s="46"/>
       <c r="D27" s="46"/>
       <c r="E27" s="46"/>
     </row>
     <row r="28" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="80" t="s">
+      <c r="A28" s="69" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="43" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C28" s="46"/>
       <c r="D28" s="46"/>
@@ -2849,10 +2859,10 @@
     </row>
     <row r="29" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="69" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B29" s="43" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C29" s="46"/>
       <c r="D29" s="46"/>
@@ -2866,7 +2876,7 @@
         <v>21</v>
       </c>
       <c r="B30" s="43" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C30" s="46"/>
       <c r="D30" s="46"/>
@@ -2877,10 +2887,10 @@
     </row>
     <row r="31" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="70" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B31" s="71" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C31" s="46"/>
       <c r="D31" s="46"/>
@@ -2889,7 +2899,7 @@
     <row r="32" spans="1:9" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A32" s="17"/>
       <c r="B32" s="18" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C32" s="9" t="e">
         <f t="shared" ref="C32:E32" si="1">AVERAGE(C25:C31)</f>
@@ -2906,7 +2916,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B33" s="18" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C33" s="26" t="e">
         <f>C32/10</f>
@@ -2924,7 +2934,7 @@
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="61"/>
       <c r="B35" s="61" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C35" s="61"/>
       <c r="D35" s="61"/>
@@ -2932,7 +2942,7 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B36" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C36" s="19" t="e">
         <f>(C19*0.5 +C32* 0.5)/10</f>
@@ -2950,7 +2960,7 @@
     <row r="37" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A37" s="29"/>
       <c r="B37" s="72" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C37" s="13" t="e">
         <f>AVERAGE(C36:E36)</f>
@@ -3010,7 +3020,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="2">
+  <dataValidations disablePrompts="1" count="2">
     <dataValidation type="decimal" errorStyle="information" allowBlank="1" showErrorMessage="1" errorTitle="Out of range" error="Enter value between 1 and 5" promptTitle="Score Range" prompt="Between 1 and 5" sqref="C12:E18" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>0</formula1>
       <formula2>10</formula2>
@@ -3021,8 +3031,8 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="B22" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
-    <hyperlink ref="B8" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="B22" r:id="rId1" display="Part 2 - Poster Presentation (guidelines) - 30%" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="B8" r:id="rId2" display="Part 1 - Written Report (guidelines) - 70%" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
     <hyperlink ref="B9" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
     <hyperlink ref="B23" r:id="rId4" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
   </hyperlinks>
@@ -3045,29 +3055,29 @@
   <sheetData>
     <row r="1" spans="1:2" ht="23" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B5" s="2"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="36" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="38" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
@@ -3075,74 +3085,74 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="33" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="39" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B12" s="47"/>
     </row>
     <row r="13" spans="1:2" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="39" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B13" s="47"/>
     </row>
     <row r="14" spans="1:2" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="39" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="B14" s="47"/>
     </row>
     <row r="15" spans="1:2" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="39" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B15" s="47"/>
     </row>
     <row r="16" spans="1:2" ht="34" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="39" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B16" s="47"/>
     </row>
     <row r="17" spans="1:2" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="39" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B17" s="47"/>
     </row>
     <row r="18" spans="1:2" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="39" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B18" s="47"/>
     </row>
     <row r="19" spans="1:2" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="39" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B19" s="47"/>
     </row>
     <row r="20" spans="1:2" ht="34" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="39" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="B20" s="47"/>
     </row>
     <row r="21" spans="1:2" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="39" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B21" s="47"/>
     </row>
@@ -3157,7 +3167,7 @@
     </row>
     <row r="23" spans="1:2" ht="35" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A23" s="41" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B23" s="42" t="e">
         <f>B22*5</f>
@@ -3196,7 +3206,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="54.42578125" customWidth="1"/>
@@ -3210,22 +3220,22 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="36" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="38" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
@@ -3233,38 +3243,38 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="34" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="39" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B12" s="47"/>
     </row>
     <row r="13" spans="1:2" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="39" t="s">
-        <v>84</v>
+        <v>117</v>
       </c>
       <c r="B13" s="47"/>
     </row>
     <row r="14" spans="1:2" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="39" t="s">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="B14" s="47"/>
     </row>
     <row r="15" spans="1:2" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="39" t="s">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="B15" s="47"/>
     </row>
@@ -3272,73 +3282,67 @@
       <c r="A16" s="39" t="s">
         <v>87</v>
       </c>
-      <c r="B16" s="47"/>
-    </row>
-    <row r="17" spans="1:2" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="80"/>
+    </row>
+    <row r="17" spans="1:2" ht="34" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="39" t="s">
-        <v>88</v>
-      </c>
-      <c r="B17" s="47"/>
+        <v>86</v>
+      </c>
+      <c r="B17" s="80"/>
     </row>
     <row r="18" spans="1:2" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="39" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B18" s="47"/>
     </row>
     <row r="19" spans="1:2" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="39" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="B19" s="47"/>
     </row>
     <row r="20" spans="1:2" ht="34" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="39" t="s">
-        <v>91</v>
-      </c>
-      <c r="B20" s="47"/>
+        <v>116</v>
+      </c>
+      <c r="B20" s="80"/>
     </row>
     <row r="21" spans="1:2" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="39" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B21" s="47"/>
     </row>
     <row r="22" spans="1:2" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="39" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B22" s="47"/>
     </row>
     <row r="23" spans="1:2" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="39" t="s">
-        <v>94</v>
-      </c>
-      <c r="B23" s="47"/>
-    </row>
-    <row r="24" spans="1:2" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="12" t="s">
+      <c r="A23" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="B24" s="8" t="e">
-        <f>SUM(B12:B23)/COUNT(B12:B23)</f>
+      <c r="B23" s="8" t="e">
+        <f>SUM(B12:B22)/COUNT(B12:B22)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="41" t="s">
-        <v>95</v>
-      </c>
-      <c r="B25" s="42" t="e">
-        <f>B24*5</f>
+    <row r="24" spans="1:2" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="41" t="s">
+        <v>90</v>
+      </c>
+      <c r="B24" s="42" t="e">
+        <f>B23*5</f>
         <v>#DIV/0!</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection sheet="1" selectLockedCells="1"/>
   <phoneticPr fontId="9" type="noConversion"/>
-  <conditionalFormatting sqref="B12:B23">
-    <cfRule type="colorScale" priority="18">
+  <conditionalFormatting sqref="B12:B22">
+    <cfRule type="colorScale" priority="21">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3350,7 +3354,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="decimal" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Score out of range" error="Score range: 0-1" promptTitle="Score Range" prompt="Range: 0 - 1" sqref="B12:B23" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="decimal" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Score out of range" error="Score range: 0-1" promptTitle="Score Range" prompt="Range: 0 - 1" sqref="B12:B22" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
